--- a/Data/Project_Pan.xlsx
+++ b/Data/Project_Pan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b251ae8028ef8773/Documentos/Data Analysis practice/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\MakeupProjectPan\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1288" documentId="11_F25DC773A252ABDACC104815991A67F25ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38359E21-5FC4-4D44-9563-A698FE8A88AF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7DF09CB-4B1E-4F61-A331-7C5196364CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1620" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="298">
   <si>
     <t>ProductName</t>
   </si>
@@ -914,6 +914,27 @@
   </si>
   <si>
     <t>1 Very light</t>
+  </si>
+  <si>
+    <t>P067</t>
+  </si>
+  <si>
+    <t>Mac</t>
+  </si>
+  <si>
+    <t>P068</t>
+  </si>
+  <si>
+    <t>Urban Decay</t>
+  </si>
+  <si>
+    <t>P069</t>
+  </si>
+  <si>
+    <t>Setting Powder</t>
+  </si>
+  <si>
+    <t>01 Sugar serve</t>
   </si>
 </sst>
 </file>
@@ -1004,7 +1025,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1022,11 +1043,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="22">
     <dxf>
       <fill>
         <patternFill>
@@ -1047,6 +1069,40 @@
           <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1412,12 +1468,6 @@
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1431,13 +1481,9 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{ACFC25FF-BC78-4B46-B0E7-E3DC147CF5AF}" name="Products" displayName="Products" ref="A1:R67" totalsRowShown="0" headerRowDxfId="17">
-  <autoFilter ref="A1:R67" xr:uid="{ACFC25FF-BC78-4B46-B0E7-E3DC147CF5AF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{ACFC25FF-BC78-4B46-B0E7-E3DC147CF5AF}" name="Products" displayName="Products" ref="A1:R70" totalsRowShown="0" headerRowDxfId="8">
+  <autoFilter ref="A1:R70" xr:uid="{ACFC25FF-BC78-4B46-B0E7-E3DC147CF5AF}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{5A8A122B-541F-482F-A329-30E536EC3342}" name="ProductID"/>
     <tableColumn id="2" xr3:uid="{E025A529-F994-4B68-B249-993CAB28BD7B}" name="ProductName"/>
@@ -1453,7 +1499,7 @@
     <tableColumn id="9" xr3:uid="{D3D8549C-90E0-417A-850A-E9057244809C}" name="Store"/>
     <tableColumn id="10" xr3:uid="{D35F3E31-E49A-4E0E-AC37-0E376B4CFAF7}" name="PurchaseReason"/>
     <tableColumn id="11" xr3:uid="{630DF184-9588-4A31-AE43-5893B739CD5E}" name="OpenedDate"/>
-    <tableColumn id="12" xr3:uid="{AC2D5B29-7AE2-485C-B244-8A6694B80410}" name="ExpiryMonthsAfterOpening" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{AC2D5B29-7AE2-485C-B244-8A6694B80410}" name="ExpiryMonthsAfterOpening" dataDxfId="7"/>
     <tableColumn id="13" xr3:uid="{B2046ECE-B9AD-47BB-A789-EE194A1C8477}" name="Status"/>
     <tableColumn id="14" xr3:uid="{2B0CC3FE-00F1-415E-BAB7-6D274DB9A287}" name="FinishedDate"/>
     <tableColumn id="20" xr3:uid="{85EB2270-E1A0-4E33-BAD3-6832CEDD6104}" name="Decluterred"/>
@@ -1463,17 +1509,17 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{33BBAF23-26BF-4147-B6CE-000FF151FA45}" name="UsageLog" displayName="UsageLog" ref="A1:H67" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
-  <autoFilter ref="A1:H67" xr:uid="{33BBAF23-26BF-4147-B6CE-000FF151FA45}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{33BBAF23-26BF-4147-B6CE-000FF151FA45}" name="UsageLog" displayName="UsageLog" ref="A1:H68" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18" totalsRowBorderDxfId="17">
+  <autoFilter ref="A1:H68" xr:uid="{33BBAF23-26BF-4147-B6CE-000FF151FA45}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{192920FB-897E-4386-8D1D-10C900F4E6CE}" name="ProductID" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{5FA32629-6E43-465F-95D8-A3AD775DE7C0}" name="ProductName" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{18D5C2E7-5381-4F5F-825A-844C594A4F11}" name="Brand" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{F8DCC179-BEED-4A3C-8714-720D018C30C4}" name="Category" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{599B67A9-862E-41D4-8CA2-A8326FF95ADD}" name="ProductType" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{F93A29E8-B380-44A8-933E-7CABCABDC2C0}" name="ProductDetail" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{1B0F38AD-9560-450E-BC22-ADCC50557DF0}" name="Shade" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{BDF0D2D1-8574-4C4C-BB4B-9E4D734DAE64}" name="UsesSeptember" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{192920FB-897E-4386-8D1D-10C900F4E6CE}" name="ProductID" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{5FA32629-6E43-465F-95D8-A3AD775DE7C0}" name="ProductName" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{18D5C2E7-5381-4F5F-825A-844C594A4F11}" name="Brand" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{F8DCC179-BEED-4A3C-8714-720D018C30C4}" name="Category" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{599B67A9-862E-41D4-8CA2-A8326FF95ADD}" name="ProductType" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{F93A29E8-B380-44A8-933E-7CABCABDC2C0}" name="ProductDetail" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{1B0F38AD-9560-450E-BC22-ADCC50557DF0}" name="Shade" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{BDF0D2D1-8574-4C4C-BB4B-9E4D734DAE64}" name="UsesSeptember" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1742,7 +1788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R67"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -5197,8 +5243,11 @@
       <c r="P65" t="s">
         <v>66</v>
       </c>
+      <c r="Q65" s="3">
+        <v>46303</v>
+      </c>
       <c r="R65" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.35">
@@ -5307,10 +5356,166 @@
         <v>125</v>
       </c>
     </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>291</v>
+      </c>
+      <c r="B68" t="s">
+        <v>60</v>
+      </c>
+      <c r="C68" t="s">
+        <v>292</v>
+      </c>
+      <c r="D68" t="s">
+        <v>16</v>
+      </c>
+      <c r="E68" t="s">
+        <v>60</v>
+      </c>
+      <c r="F68" t="s">
+        <v>29</v>
+      </c>
+      <c r="G68" t="s">
+        <v>198</v>
+      </c>
+      <c r="H68">
+        <v>30</v>
+      </c>
+      <c r="I68" t="s">
+        <v>69</v>
+      </c>
+      <c r="J68" s="3">
+        <v>46304</v>
+      </c>
+      <c r="K68">
+        <v>33</v>
+      </c>
+      <c r="L68" t="s">
+        <v>175</v>
+      </c>
+      <c r="M68" t="s">
+        <v>176</v>
+      </c>
+      <c r="N68" s="3">
+        <v>46304</v>
+      </c>
+      <c r="O68" s="4">
+        <v>12</v>
+      </c>
+      <c r="P68" t="s">
+        <v>66</v>
+      </c>
+      <c r="R68" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>293</v>
+      </c>
+      <c r="B69" t="s">
+        <v>60</v>
+      </c>
+      <c r="C69" t="s">
+        <v>294</v>
+      </c>
+      <c r="D69" t="s">
+        <v>16</v>
+      </c>
+      <c r="E69" t="s">
+        <v>60</v>
+      </c>
+      <c r="F69" t="s">
+        <v>29</v>
+      </c>
+      <c r="G69" t="s">
+        <v>198</v>
+      </c>
+      <c r="H69">
+        <v>15</v>
+      </c>
+      <c r="I69" t="s">
+        <v>69</v>
+      </c>
+      <c r="J69" s="3">
+        <v>46307</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69" t="s">
+        <v>175</v>
+      </c>
+      <c r="M69" t="s">
+        <v>140</v>
+      </c>
+      <c r="O69" s="4">
+        <v>6</v>
+      </c>
+      <c r="P69" t="s">
+        <v>135</v>
+      </c>
+      <c r="R69" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>295</v>
+      </c>
+      <c r="B70" t="s">
+        <v>296</v>
+      </c>
+      <c r="C70" t="s">
+        <v>156</v>
+      </c>
+      <c r="D70" t="s">
+        <v>16</v>
+      </c>
+      <c r="E70" t="s">
+        <v>33</v>
+      </c>
+      <c r="F70" t="s">
+        <v>34</v>
+      </c>
+      <c r="G70" t="s">
+        <v>297</v>
+      </c>
+      <c r="H70">
+        <v>6</v>
+      </c>
+      <c r="I70" t="s">
+        <v>122</v>
+      </c>
+      <c r="J70" s="3">
+        <v>46307</v>
+      </c>
+      <c r="K70">
+        <v>12</v>
+      </c>
+      <c r="L70" t="s">
+        <v>160</v>
+      </c>
+      <c r="M70" t="s">
+        <v>176</v>
+      </c>
+      <c r="N70" s="3">
+        <v>46310</v>
+      </c>
+      <c r="O70" s="4">
+        <v>12</v>
+      </c>
+      <c r="P70" t="s">
+        <v>66</v>
+      </c>
+      <c r="R70" t="s">
+        <v>125</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A2:P67">
-    <cfRule type="expression" dxfId="2" priority="3">
+  <conditionalFormatting sqref="A2:P70">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>ISBLANK(A2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5325,25 +5530,25 @@
           <x14:formula1>
             <xm:f>Dropdownlists!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D67</xm:sqref>
+          <xm:sqref>D2:D70</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{47FAEE91-1E0A-4BD8-8B60-544AFB047C58}">
           <x14:formula1>
             <xm:f>Dropdownlists!$D:$D</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E67</xm:sqref>
+          <xm:sqref>E2:E70</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2D1D2F79-1A2E-4F21-BB79-D756E54D8885}">
           <x14:formula1>
             <xm:f>Dropdownlists!$G:$G</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F67</xm:sqref>
+          <xm:sqref>F2:F70</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{83474B4B-7A85-4C9F-8371-114069738CA7}">
           <x14:formula1>
             <xm:f>Dropdownlists!$J:$J</xm:f>
           </x14:formula1>
-          <xm:sqref>R2:R67</xm:sqref>
+          <xm:sqref>R2:R70</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5353,7 +5558,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE61EB1-A41C-4893-B079-2ECCBB28D414}">
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
@@ -5440,7 +5645,7 @@
         <v>121</v>
       </c>
       <c r="H3" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -5596,7 +5801,7 @@
         <v>2</v>
       </c>
       <c r="H9" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -5648,7 +5853,7 @@
         <v>149</v>
       </c>
       <c r="H11" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -5674,7 +5879,7 @@
         <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -5700,7 +5905,7 @@
         <v>100</v>
       </c>
       <c r="H13" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -5752,7 +5957,7 @@
         <v>166</v>
       </c>
       <c r="H15" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -5778,7 +5983,7 @@
         <v>170</v>
       </c>
       <c r="H16" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -5804,7 +6009,7 @@
         <v>168</v>
       </c>
       <c r="H17" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
@@ -6012,7 +6217,7 @@
         <v>30</v>
       </c>
       <c r="H25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
@@ -6064,7 +6269,7 @@
         <v>190</v>
       </c>
       <c r="H27" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
@@ -6090,7 +6295,7 @@
         <v>192</v>
       </c>
       <c r="H28" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
@@ -6142,7 +6347,7 @@
         <v>197</v>
       </c>
       <c r="H30" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
@@ -6168,7 +6373,7 @@
         <v>203</v>
       </c>
       <c r="H31" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -6220,7 +6425,7 @@
         <v>206</v>
       </c>
       <c r="H33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
@@ -6246,7 +6451,7 @@
         <v>205</v>
       </c>
       <c r="H34" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
@@ -6272,7 +6477,7 @@
         <v>209</v>
       </c>
       <c r="H35" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
@@ -6324,7 +6529,7 @@
         <v>212</v>
       </c>
       <c r="H37" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
@@ -6350,7 +6555,7 @@
         <v>213</v>
       </c>
       <c r="H38" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
@@ -6402,7 +6607,7 @@
         <v>221</v>
       </c>
       <c r="H40" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
@@ -6428,7 +6633,7 @@
         <v>222</v>
       </c>
       <c r="H41" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
@@ -6454,7 +6659,7 @@
         <v>221</v>
       </c>
       <c r="H42" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -6480,7 +6685,7 @@
         <v>224</v>
       </c>
       <c r="H43" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -6506,7 +6711,7 @@
         <v>227</v>
       </c>
       <c r="H44" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -6532,7 +6737,7 @@
         <v>228</v>
       </c>
       <c r="H45" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
@@ -6558,7 +6763,7 @@
         <v>231</v>
       </c>
       <c r="H46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
@@ -6610,7 +6815,7 @@
         <v>259</v>
       </c>
       <c r="H48" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
@@ -6636,7 +6841,7 @@
         <v>261</v>
       </c>
       <c r="H49" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
@@ -6714,7 +6919,7 @@
         <v>263</v>
       </c>
       <c r="H52" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
@@ -6740,7 +6945,7 @@
         <v>265</v>
       </c>
       <c r="H53" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
@@ -6766,7 +6971,7 @@
         <v>269</v>
       </c>
       <c r="H54" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
@@ -6844,7 +7049,7 @@
         <v>272</v>
       </c>
       <c r="H57" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
@@ -6896,7 +7101,7 @@
         <v>275</v>
       </c>
       <c r="H59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
@@ -6948,7 +7153,7 @@
         <v>198</v>
       </c>
       <c r="H61" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
@@ -7052,7 +7257,7 @@
         <v>216</v>
       </c>
       <c r="H65" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
@@ -7078,7 +7283,7 @@
         <v>286</v>
       </c>
       <c r="H66" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
@@ -7104,18 +7309,49 @@
         <v>290</v>
       </c>
       <c r="H67" s="8">
-        <v>0</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A68" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="H68" s="9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:G67">
-    <cfRule type="expression" dxfId="1" priority="1">
+  <conditionalFormatting sqref="A2:G68">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>ISBLANK(A2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H67">
-    <cfRule type="expression" dxfId="0" priority="2">
+  <conditionalFormatting sqref="H2:H68">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>ISBLANK(H2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A68:G68">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>ISBLANK(A68)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7129,19 +7365,19 @@
           <x14:formula1>
             <xm:f>Dropdownlists!$G:$G</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F67</xm:sqref>
+          <xm:sqref>F2:F68</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A2A04BBC-D6C8-4B34-962C-F6E2DFF1F9B3}">
           <x14:formula1>
             <xm:f>Dropdownlists!$D:$D</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E67</xm:sqref>
+          <xm:sqref>E2:E68</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CB60DF21-745D-45DB-B934-D8CFEFFC73CA}">
           <x14:formula1>
             <xm:f>Dropdownlists!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D67</xm:sqref>
+          <xm:sqref>D2:D68</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
